--- a/ViidooDBServiceAPI/templates/Purchase_Request_Form.xlsx
+++ b/ViidooDBServiceAPI/templates/Purchase_Request_Form.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\linhdh\Sigma_giấy tờ\data tech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jobs\Sigma-Project\SVNPortal\ViidooDBServiceAPI\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433B8DA5-3BCC-4043-AD1D-1F3E6A2C3DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B0D77E-63EB-4005-8F1C-D5CB3F64B906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Format" sheetId="12" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>YÊU CẦU MUA HÀNG</t>
   </si>
@@ -116,13 +116,7 @@
     <t>SVF-PU-002 rev 01</t>
   </si>
   <si>
-    <t>pcs</t>
-  </si>
-  <si>
     <t>Total Amount</t>
-  </si>
-  <si>
-    <t>Monitor HP P204v 19.5-inch</t>
   </si>
   <si>
     <r>
@@ -158,18 +152,6 @@
       </rPr>
       <t>: IT</t>
     </r>
-  </si>
-  <si>
-    <t>Tivi Hisense FHD 43 inch 43A4N</t>
-  </si>
-  <si>
-    <t>Pouch &amp; Sling &amp;Twist</t>
-  </si>
-  <si>
-    <t>Sling &amp;Twist</t>
-  </si>
-  <si>
-    <t>43-inch TV mount</t>
   </si>
 </sst>
 </file>
@@ -629,8 +611,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="118848" y="4143663"/>
-          <a:ext cx="11162007" cy="1896245"/>
+          <a:off x="118848" y="4171180"/>
+          <a:ext cx="10861440" cy="1851795"/>
           <a:chOff x="174171" y="4208234"/>
           <a:chExt cx="8541558" cy="1543566"/>
         </a:xfrm>
@@ -1628,18 +1610,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
-    <col min="2" max="2" width="40.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="34.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="40.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="15.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11"/>
       <c r="B1" s="27" t="s">
         <v>17</v>
@@ -1655,7 +1637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="29" t="s">
         <v>18</v>
@@ -1669,7 +1651,7 @@
       </c>
       <c r="H2" s="24"/>
     </row>
-    <row r="3" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
         <v>0</v>
       </c>
@@ -1683,7 +1665,7 @@
       </c>
       <c r="H3" s="25"/>
     </row>
-    <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
         <v>1</v>
       </c>
@@ -1697,9 +1679,9 @@
       </c>
       <c r="H4" s="26"/>
     </row>
-    <row r="5" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
@@ -1709,7 +1691,7 @@
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
     </row>
-    <row r="6" spans="1:8" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
@@ -1735,7 +1717,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="6" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" s="6" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -1761,84 +1743,54 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="6" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="18">
-        <v>2</v>
-      </c>
-      <c r="F8" s="14">
-        <v>2106000</v>
-      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="14"/>
       <c r="G8" s="14">
         <f>F8*E8</f>
-        <v>4212000</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" spans="1:8" s="6" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" s="6" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="18">
-        <v>3</v>
-      </c>
-      <c r="F9" s="14">
-        <v>700000</v>
-      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="14"/>
       <c r="G9" s="14">
         <f>F9*E9</f>
-        <v>2100000</v>
+        <v>0</v>
       </c>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="1:8" s="6" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" s="6" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="18">
-        <v>3</v>
-      </c>
-      <c r="F10" s="14">
-        <v>6524000</v>
-      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="14"/>
       <c r="G10" s="14">
         <f t="shared" ref="G10" si="0">F10*E10</f>
-        <v>19572000</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -1847,11 +1799,11 @@
       <c r="F11" s="21"/>
       <c r="G11" s="16">
         <f>SUM(G8:G10)</f>
-        <v>25884000</v>
+        <v>0</v>
       </c>
       <c r="H11" s="15"/>
     </row>
-    <row r="13" spans="1:8" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:8" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A11:F11"/>
@@ -1870,7 +1822,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283461" right="0.70866141732283461" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="78" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>